--- a/output/pdf_financials_xlsx/BYL.xlsx
+++ b/output/pdf_financials_xlsx/BYL.xlsx
@@ -5248,13 +5248,13 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>3.193</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>3.672</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>3.688</v>
       </c>
       <c r="E91" s="3" t="n">
         <v>2.849</v>
@@ -5300,43 +5300,43 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.866</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.446</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.798</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.715</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.426</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.525</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.728</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>9.313000000000001</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.998</v>
       </c>
     </row>
     <row r="93">
@@ -11140,7 +11140,11 @@
           <t>Share-based payment reserve 23</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -13724,7 +13728,11 @@
           <t>Share-based payment reserve 22</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -15864,7 +15872,11 @@
           <t>Share-based payment reserve Note 22</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -16702,7 +16714,11 @@
           <t>Share-based payment reserve Note 22</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -17550,7 +17566,11 @@
           <t>Share-based payment reserve Note 22</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -20010,7 +20030,11 @@
           <t>Share-based payment reserve Note 23</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -21556,7 +21580,11 @@
           <t>Share-based payment reserve Note 21</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -23208,7 +23236,11 @@
           <t>Share-based payments reserve (note 17) 1,446</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -24744,7 +24776,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -26006,7 +26042,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -26174,7 +26214,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -26588,7 +26632,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -27778,7 +27826,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E229" s="5" t="n">
         <v>3.193</v>
       </c>

--- a/output/pdf_financials_xlsx/BYL.xlsx
+++ b/output/pdf_financials_xlsx/BYL.xlsx
@@ -3043,22 +3043,22 @@
         <v>8.189</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>8.678000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0</v>
+        <v>23.512</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0</v>
+        <v>21.088</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0</v>
+        <v>19.669</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0</v>
+        <v>15.831</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0</v>
+        <v>18.37</v>
       </c>
       <c r="M47" s="3" t="n">
         <v>17.623</v>
@@ -3092,22 +3092,22 @@
         <v>1.467</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.662</v>
+        <v>4.252</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>29.691</v>
+        <v>6.179</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>30.876</v>
+        <v>9.788</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>26.489</v>
+        <v>6.82</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>21.18</v>
+        <v>3.753</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>22.78</v>
+        <v>3.858</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>3.959</v>
@@ -3616,16 +3616,16 @@
         <v>27.371</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>19.359</v>
+        <v>33.868</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>23.658</v>
+        <v>36.327</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>12.491</v>
+        <v>22.262</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>10.344</v>
+        <v>19.458</v>
       </c>
       <c r="M58" s="3" t="n">
         <v>12.211</v>
@@ -3711,13 +3711,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0</v>
+        <v>31.601</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0</v>
+        <v>18.908</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0</v>
+        <v>15.908</v>
       </c>
       <c r="K60" s="3" t="n">
         <v>0</v>
@@ -3763,16 +3763,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>63.905</v>
+        <v>3.126</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>51.794</v>
+        <v>0.727</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>19.456</v>
+        <v>0.214</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>13.587</v>
+        <v>0.079</v>
       </c>
       <c r="M61" s="3" t="n">
         <v>1.171</v>
@@ -5108,22 +5108,22 @@
         <v>85.837</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>90.929</v>
+        <v>109.21</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>136.675</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>137.195</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>142.16</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>172.7</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0</v>
+        <v>172.79</v>
       </c>
       <c r="M88" s="3" t="n">
         <v>187.767</v>
@@ -13982,7 +13982,11 @@
           <t>Inventories Note 8</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -14060,7 +14064,11 @@
           <t>Assets held for sale Note 13</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AssetsHeldForSale</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -14144,7 +14152,11 @@
           <t>Other current assets Note 7</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OtherCurrentAssets</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -14372,7 +14384,11 @@
           <t>Right of use assets Note 10</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -14606,7 +14622,11 @@
           <t>Other long-term assets Note 11</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>OtherNonCurrentAssets</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -15078,7 +15098,11 @@
           <t>Liabilities related to assets held for sale Note 13</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AssetsHeldForSale</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -15164,7 +15188,11 @@
           <t>Income tax payable Note 20</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>IncomeTaxPayable</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -15788,7 +15816,11 @@
           <t>Share capital Note 21</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -16630,7 +16662,11 @@
           <t>Share capital Note 21</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -17146,7 +17182,11 @@
           <t>Assets held for sale Note 12</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AssetsHeldForSale</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -17232,7 +17272,11 @@
           <t>Deferred tax assets Note 20</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>DeferredTaxAssets</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -17316,7 +17360,11 @@
           <t>Goodwill Note 13</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -17484,7 +17532,11 @@
           <t>Share capital Note 21</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -17992,7 +18044,11 @@
           <t>Goodwill Note 12</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -18502,7 +18558,11 @@
           <t>Other current assets Note 8</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>OtherCurrentAssets</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -18584,7 +18644,11 @@
           <t>Inventories Note 9</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -18754,7 +18818,11 @@
           <t>Right of use assets Note 11</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -18840,7 +18908,11 @@
           <t>Other long-term assets Note 12</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>OtherNonCurrentAssets</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -18924,7 +18996,11 @@
           <t>Deferred tax assets Note 21</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DeferredTaxAssets</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -19348,7 +19424,11 @@
           <t>Income tax payable Note 21</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>IncomeTaxPayable</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -19946,7 +20026,11 @@
           <t>Share capital Note 22</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -20470,7 +20554,11 @@
           <t>Deferred tax assets Note 19</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DeferredTaxAssets</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -20728,7 +20816,11 @@
           <t>Goodwill Note 6, 11</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -21496,7 +21588,11 @@
           <t>Share capital Note 20</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
